--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D93C996-7979-49F3-9C0E-967EEB2AE235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E610AD-1073-4316-B77E-5D5E6AEEED71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="64">
   <si>
     <t>Date</t>
   </si>
@@ -66,34 +66,37 @@
     <t>SM-464</t>
   </si>
   <si>
+    <t>Nile Air NP-252</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-161</t>
+  </si>
+  <si>
+    <t>Nile Air NP-152</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
+  </si>
+  <si>
     <t>Nile Air NP-154</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>Nile Air NP-152</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-161</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
     <t>MED</t>
   </si>
   <si>
     <t>06-AUG-26</t>
   </si>
   <si>
-    <t>EgyptAir MS-650</t>
+    <t>Nile Air NP-454</t>
   </si>
   <si>
     <t>10-AUG-26</t>
@@ -123,6 +126,9 @@
     <t>20-AUG-26</t>
   </si>
   <si>
+    <t>Nile Air NP-156</t>
+  </si>
+  <si>
     <t>24-AUG-26</t>
   </si>
   <si>
@@ -132,58 +138,52 @@
     <t>31-AUG-26</t>
   </si>
   <si>
-    <t>Nile Air NP-252</t>
-  </si>
-  <si>
     <t>03-SEP-26</t>
   </si>
   <si>
+    <t>EgyptAir MS-652</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-648</t>
+  </si>
+  <si>
+    <t>10-SEP-26</t>
+  </si>
+  <si>
+    <t>14-SEP-26</t>
+  </si>
+  <si>
+    <t>17-SEP-26</t>
+  </si>
+  <si>
+    <t>21-SEP-26</t>
+  </si>
+  <si>
+    <t>24-SEP-26</t>
+  </si>
+  <si>
     <t>flynas XY-279</t>
   </si>
   <si>
-    <t>EgyptAir MS-652</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-648</t>
-  </si>
-  <si>
-    <t>10-SEP-26</t>
-  </si>
-  <si>
-    <t>14-SEP-26</t>
-  </si>
-  <si>
-    <t>17-SEP-26</t>
-  </si>
-  <si>
-    <t>21-SEP-26</t>
-  </si>
-  <si>
-    <t>24-SEP-26</t>
-  </si>
-  <si>
-    <t>28-SEP-26</t>
-  </si>
-  <si>
     <t>01-OCT-26</t>
   </si>
   <si>
     <t>Air Arabia Egypt E5-411</t>
   </si>
   <si>
+    <t>flynas XY-265</t>
+  </si>
+  <si>
+    <t>flynas XY-273</t>
+  </si>
+  <si>
     <t>05-OCT-26</t>
   </si>
   <si>
-    <t>flynas XY-265</t>
-  </si>
-  <si>
     <t>08-OCT-26</t>
   </si>
   <si>
-    <t>12-OCT-26</t>
-  </si>
-  <si>
-    <t>flynas XY-273</t>
+    <t>flynas XY-267</t>
   </si>
   <si>
     <t>15-OCT-26</t>
@@ -192,64 +192,31 @@
     <t>19-OCT-26</t>
   </si>
   <si>
-    <t>22-OCT-26</t>
+    <t>25-OCT-26</t>
+  </si>
+  <si>
+    <t>flynas XY-287</t>
+  </si>
+  <si>
+    <t>flynas XY-269</t>
   </si>
   <si>
     <t>27-OCT-26</t>
   </si>
   <si>
-    <t>flynas XY-267</t>
-  </si>
-  <si>
     <t>29-OCT-26</t>
   </si>
   <si>
-    <t>22-NOV-26</t>
-  </si>
-  <si>
-    <t>29-NOV-26</t>
-  </si>
-  <si>
-    <t>flynas XY-287</t>
-  </si>
-  <si>
-    <t>01-DEC-26</t>
-  </si>
-  <si>
-    <t>06-DEC-26</t>
-  </si>
-  <si>
-    <t>08-DEC-26</t>
-  </si>
-  <si>
-    <t>flynas XY-263</t>
-  </si>
-  <si>
-    <t>10-DEC-26</t>
-  </si>
-  <si>
-    <t>15-DEC-26</t>
-  </si>
-  <si>
-    <t>17-DEC-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-321</t>
-  </si>
-  <si>
-    <t>20-DEC-26</t>
+    <t>24-NOV-26</t>
+  </si>
+  <si>
+    <t>flynas XY-275</t>
   </si>
   <si>
     <t>22-DEC-26</t>
   </si>
   <si>
-    <t>flynas XY-271</t>
-  </si>
-  <si>
-    <t>29-DEC-26</t>
-  </si>
-  <si>
-    <t>31-DEC-26</t>
+    <t>24-DEC-26</t>
   </si>
 </sst>
 </file>
@@ -646,7 +613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -733,22 +700,22 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="E3" s="2">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="F3" s="2">
-        <v>-187</v>
+        <v>-228</v>
       </c>
       <c r="G3" s="2">
         <v>40</v>
@@ -768,22 +735,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>365</v>
+        <v>501</v>
       </c>
       <c r="E4" s="2">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="F4" s="2">
-        <v>-187</v>
+        <v>-143</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -803,22 +770,22 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
-        <v>414</v>
+        <v>365</v>
       </c>
       <c r="E5" s="2">
         <v>644</v>
       </c>
       <c r="F5" s="2">
-        <v>-230</v>
+        <v>-279</v>
       </c>
       <c r="G5" s="2">
         <v>40</v>
@@ -829,8 +796,8 @@
       <c r="I5" s="2">
         <v>-10</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -838,22 +805,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="2">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="E6" s="2">
         <v>644</v>
       </c>
       <c r="F6" s="2">
-        <v>-228</v>
+        <v>-279</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -864,8 +831,8 @@
       <c r="I6" s="2">
         <v>-10</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -879,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2">
         <v>365</v>
@@ -900,7 +867,7 @@
         <v>-10</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -908,13 +875,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <v>365</v>
@@ -935,7 +902,7 @@
         <v>-10</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -943,13 +910,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2">
         <v>365</v>
@@ -970,7 +937,7 @@
         <v>-10</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -978,13 +945,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2">
         <v>365</v>
@@ -1005,7 +972,7 @@
         <v>-10</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -1013,22 +980,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
         <v>365</v>
       </c>
       <c r="E11" s="2">
-        <v>644</v>
+        <v>552</v>
       </c>
       <c r="F11" s="2">
-        <v>-279</v>
+        <v>-187</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -1039,8 +1006,8 @@
       <c r="I11" s="2">
         <v>-10</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>20</v>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -1048,34 +1015,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2">
-        <v>439</v>
+        <v>365</v>
       </c>
       <c r="E12" s="2">
-        <v>644</v>
+        <v>552</v>
       </c>
       <c r="F12" s="2">
-        <v>-205</v>
+        <v>-187</v>
       </c>
       <c r="G12" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>20</v>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1083,31 +1050,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="E13" s="2">
         <v>552</v>
       </c>
       <c r="F13" s="2">
-        <v>-187</v>
+        <v>-121</v>
       </c>
       <c r="G13" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>14</v>
@@ -1118,13 +1085,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2">
         <v>365</v>
@@ -1153,31 +1120,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>431</v>
+        <v>365</v>
       </c>
       <c r="E15" s="2">
         <v>552</v>
       </c>
       <c r="F15" s="2">
-        <v>-121</v>
+        <v>-187</v>
       </c>
       <c r="G15" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2">
         <v>30</v>
       </c>
       <c r="I15" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>14</v>
@@ -1188,22 +1155,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
         <v>365</v>
       </c>
       <c r="E16" s="2">
-        <v>506</v>
+        <v>552</v>
       </c>
       <c r="F16" s="2">
-        <v>-141</v>
+        <v>-187</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1223,13 +1190,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2">
         <v>365</v>
@@ -1258,13 +1225,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2">
         <v>365</v>
@@ -1293,13 +1260,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2">
         <v>365</v>
@@ -1328,22 +1295,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2">
         <v>365</v>
       </c>
       <c r="E20" s="2">
-        <v>506</v>
+        <v>703</v>
       </c>
       <c r="F20" s="2">
-        <v>-141</v>
+        <v>-338</v>
       </c>
       <c r="G20" s="2">
         <v>40</v>
@@ -1354,8 +1321,8 @@
       <c r="I20" s="2">
         <v>-10</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
+      <c r="J20" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1363,22 +1330,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D21" s="2">
         <v>365</v>
       </c>
       <c r="E21" s="2">
-        <v>506</v>
+        <v>703</v>
       </c>
       <c r="F21" s="2">
-        <v>-141</v>
+        <v>-338</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1389,8 +1356,8 @@
       <c r="I21" s="2">
         <v>-10</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>14</v>
+      <c r="J21" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1398,22 +1365,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
         <v>365</v>
       </c>
       <c r="E22" s="2">
-        <v>552</v>
+        <v>703</v>
       </c>
       <c r="F22" s="2">
-        <v>-187</v>
+        <v>-338</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1424,8 +1391,8 @@
       <c r="I22" s="2">
         <v>-10</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>14</v>
+      <c r="J22" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1433,22 +1400,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2">
         <v>365</v>
       </c>
       <c r="E23" s="2">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="F23" s="2">
-        <v>-187</v>
+        <v>-279</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1459,8 +1426,8 @@
       <c r="I23" s="2">
         <v>-10</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>14</v>
+      <c r="J23" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1468,22 +1435,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2">
         <v>365</v>
       </c>
       <c r="E24" s="2">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="F24" s="2">
-        <v>-187</v>
+        <v>-279</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1494,8 +1461,8 @@
       <c r="I24" s="2">
         <v>-10</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>14</v>
+      <c r="J24" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1509,16 +1476,16 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2">
         <v>365</v>
       </c>
       <c r="E25" s="2">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="F25" s="2">
-        <v>-187</v>
+        <v>-279</v>
       </c>
       <c r="G25" s="2">
         <v>40</v>
@@ -1529,8 +1496,8 @@
       <c r="I25" s="2">
         <v>-10</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>14</v>
+      <c r="J25" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1538,13 +1505,13 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2">
         <v>365</v>
@@ -1573,13 +1540,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2">
         <v>365</v>
@@ -1608,13 +1575,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D28" s="2">
         <v>365</v>
@@ -1643,13 +1610,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D29" s="2">
         <v>365</v>
@@ -1678,13 +1645,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D30" s="2">
         <v>365</v>
@@ -1713,13 +1680,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2">
         <v>365</v>
@@ -1748,13 +1715,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2">
         <v>365</v>
@@ -1783,13 +1750,13 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2">
         <v>365</v>
@@ -1824,16 +1791,16 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D34" s="2">
-        <v>610</v>
+        <v>365</v>
       </c>
       <c r="E34" s="2">
-        <v>673</v>
+        <v>552</v>
       </c>
       <c r="F34" s="2">
-        <v>-63</v>
+        <v>-187</v>
       </c>
       <c r="G34" s="2">
         <v>40</v>
@@ -1853,22 +1820,22 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D35" s="2">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="E35" s="2">
         <v>673</v>
       </c>
       <c r="F35" s="2">
-        <v>-29</v>
+        <v>-63</v>
       </c>
       <c r="G35" s="2">
         <v>40</v>
@@ -1888,7 +1855,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
@@ -1923,7 +1890,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
@@ -1999,7 +1966,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" s="2">
         <v>619</v>
@@ -2034,28 +2001,28 @@
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="E40" s="2">
         <v>739</v>
       </c>
       <c r="F40" s="2">
-        <v>-95</v>
+        <v>-55</v>
       </c>
       <c r="G40" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>20</v>
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2063,31 +2030,31 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D41" s="2">
-        <v>684</v>
+        <v>500</v>
       </c>
       <c r="E41" s="2">
-        <v>739</v>
+        <v>571</v>
       </c>
       <c r="F41" s="2">
-        <v>-55</v>
+        <v>-71</v>
       </c>
       <c r="G41" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>14</v>
@@ -2098,7 +2065,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
@@ -2107,13 +2074,13 @@
         <v>17</v>
       </c>
       <c r="D42" s="2">
-        <v>500</v>
+        <v>610</v>
       </c>
       <c r="E42" s="2">
-        <v>571</v>
+        <v>673</v>
       </c>
       <c r="F42" s="2">
-        <v>-71</v>
+        <v>-63</v>
       </c>
       <c r="G42" s="2">
         <v>40</v>
@@ -2139,25 +2106,25 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D43" s="2">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="E43" s="2">
-        <v>571</v>
+        <v>673</v>
       </c>
       <c r="F43" s="2">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="G43" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>14</v>
@@ -2244,7 +2211,7 @@
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D46" s="2">
         <v>644</v>
@@ -2273,31 +2240,31 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D47" s="2">
-        <v>601</v>
+        <v>676</v>
       </c>
       <c r="E47" s="2">
-        <v>571</v>
+        <v>805</v>
       </c>
       <c r="F47" s="2">
-        <v>30</v>
+        <v>-129</v>
       </c>
       <c r="G47" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2">
         <v>30</v>
       </c>
       <c r="I47" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>14</v>
@@ -2314,28 +2281,28 @@
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D48" s="2">
-        <v>586</v>
+        <v>684</v>
       </c>
       <c r="E48" s="2">
         <v>805</v>
       </c>
       <c r="F48" s="2">
-        <v>-219</v>
+        <v>-121</v>
       </c>
       <c r="G48" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>20</v>
+        <v>-10</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2349,16 +2316,16 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="E49" s="2">
         <v>805</v>
       </c>
       <c r="F49" s="2">
-        <v>-161</v>
+        <v>-121</v>
       </c>
       <c r="G49" s="2">
         <v>40</v>
@@ -2369,8 +2336,8 @@
       <c r="I49" s="2">
         <v>-10</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>20</v>
+      <c r="J49" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2378,7 +2345,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
@@ -2387,13 +2354,13 @@
         <v>47</v>
       </c>
       <c r="D50" s="2">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E50" s="2">
-        <v>805</v>
+        <v>739</v>
       </c>
       <c r="F50" s="2">
-        <v>-126</v>
+        <v>-63</v>
       </c>
       <c r="G50" s="2">
         <v>40</v>
@@ -2413,31 +2380,31 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D51" s="2">
-        <v>684</v>
+        <v>500</v>
       </c>
       <c r="E51" s="2">
-        <v>805</v>
+        <v>739</v>
       </c>
       <c r="F51" s="2">
-        <v>-121</v>
+        <v>-239</v>
       </c>
       <c r="G51" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2">
         <v>30</v>
       </c>
       <c r="I51" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>14</v>
@@ -2448,22 +2415,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D52" s="2">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="E52" s="2">
         <v>739</v>
       </c>
       <c r="F52" s="2">
-        <v>-95</v>
+        <v>-55</v>
       </c>
       <c r="G52" s="2">
         <v>40</v>
@@ -2483,31 +2450,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D53" s="2">
-        <v>679</v>
+        <v>500</v>
       </c>
       <c r="E53" s="2">
         <v>739</v>
       </c>
       <c r="F53" s="2">
-        <v>-60</v>
+        <v>-239</v>
       </c>
       <c r="G53" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>14</v>
@@ -2518,31 +2485,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2">
-        <v>500</v>
+        <v>684</v>
       </c>
       <c r="E54" s="2">
         <v>739</v>
       </c>
       <c r="F54" s="2">
-        <v>-239</v>
+        <v>-55</v>
       </c>
       <c r="G54" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>14</v>
@@ -2553,31 +2520,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D55" s="2">
-        <v>684</v>
+        <v>500</v>
       </c>
       <c r="E55" s="2">
         <v>739</v>
       </c>
       <c r="F55" s="2">
-        <v>-55</v>
+        <v>-239</v>
       </c>
       <c r="G55" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>14</v>
@@ -2588,22 +2555,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D56" s="2">
-        <v>644</v>
+        <v>524</v>
       </c>
       <c r="E56" s="2">
         <v>739</v>
       </c>
       <c r="F56" s="2">
-        <v>-95</v>
+        <v>-215</v>
       </c>
       <c r="G56" s="2">
         <v>40</v>
@@ -2623,22 +2590,22 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2">
-        <v>679</v>
+        <v>524</v>
       </c>
       <c r="E57" s="2">
         <v>739</v>
       </c>
       <c r="F57" s="2">
-        <v>-60</v>
+        <v>-215</v>
       </c>
       <c r="G57" s="2">
         <v>40</v>
@@ -2658,31 +2625,31 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D58" s="2">
-        <v>500</v>
+        <v>681</v>
       </c>
       <c r="E58" s="2">
         <v>739</v>
       </c>
       <c r="F58" s="2">
-        <v>-239</v>
+        <v>-58</v>
       </c>
       <c r="G58" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>14</v>
@@ -2693,31 +2660,31 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D59" s="2">
-        <v>676</v>
+        <v>524</v>
       </c>
       <c r="E59" s="2">
         <v>739</v>
       </c>
       <c r="F59" s="2">
-        <v>-63</v>
+        <v>-215</v>
       </c>
       <c r="G59" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>14</v>
@@ -2728,31 +2695,31 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D60" s="2">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="E60" s="2">
         <v>739</v>
       </c>
       <c r="F60" s="2">
-        <v>-55</v>
+        <v>-63</v>
       </c>
       <c r="G60" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2">
         <v>30</v>
       </c>
       <c r="I60" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>14</v>
@@ -2763,31 +2730,31 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D61" s="2">
-        <v>500</v>
+        <v>644</v>
       </c>
       <c r="E61" s="2">
         <v>739</v>
       </c>
       <c r="F61" s="2">
-        <v>-239</v>
+        <v>-95</v>
       </c>
       <c r="G61" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H61" s="2">
         <v>30</v>
       </c>
       <c r="I61" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>14</v>
@@ -2798,13 +2765,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D62" s="2">
         <v>644</v>
@@ -2824,8 +2791,8 @@
       <c r="I62" s="2">
         <v>-10</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>20</v>
+      <c r="J62" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2833,31 +2800,31 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D63" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="E63" s="2">
         <v>739</v>
       </c>
       <c r="F63" s="2">
-        <v>-63</v>
+        <v>-55</v>
       </c>
       <c r="G63" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>14</v>
@@ -2868,13 +2835,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D64" s="2">
         <v>684</v>
@@ -2886,998 +2853,18 @@
         <v>-55</v>
       </c>
       <c r="G64" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H64" s="2">
         <v>30</v>
       </c>
       <c r="I64" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D65" s="2">
-        <v>601</v>
-      </c>
-      <c r="E65" s="2">
-        <v>739</v>
-      </c>
-      <c r="F65" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G65" s="2">
-        <v>46</v>
-      </c>
-      <c r="H65" s="2">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="2">
-        <v>614</v>
-      </c>
-      <c r="E66" s="2">
-        <v>739</v>
-      </c>
-      <c r="F66" s="2">
-        <v>-125</v>
-      </c>
-      <c r="G66" s="2">
-        <v>40</v>
-      </c>
-      <c r="H66" s="2">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D67" s="2">
-        <v>614</v>
-      </c>
-      <c r="E67" s="2">
-        <v>739</v>
-      </c>
-      <c r="F67" s="2">
-        <v>-125</v>
-      </c>
-      <c r="G67" s="2">
-        <v>40</v>
-      </c>
-      <c r="H67" s="2">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D68" s="2">
-        <v>644</v>
-      </c>
-      <c r="E68" s="2">
-        <v>739</v>
-      </c>
-      <c r="F68" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G68" s="2">
-        <v>40</v>
-      </c>
-      <c r="H68" s="2">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D69" s="2">
-        <v>684</v>
-      </c>
-      <c r="E69" s="2">
-        <v>739</v>
-      </c>
-      <c r="F69" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G69" s="2">
-        <v>46</v>
-      </c>
-      <c r="H69" s="2">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D70" s="2">
-        <v>851</v>
-      </c>
-      <c r="E70" s="2">
-        <v>941</v>
-      </c>
-      <c r="F70" s="2">
-        <v>-90</v>
-      </c>
-      <c r="G70" s="2">
-        <v>46</v>
-      </c>
-      <c r="H70" s="2">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D71" s="2">
-        <v>859</v>
-      </c>
-      <c r="E71" s="2">
-        <v>941</v>
-      </c>
-      <c r="F71" s="2">
-        <v>-82</v>
-      </c>
-      <c r="G71" s="2">
-        <v>46</v>
-      </c>
-      <c r="H71" s="2">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D72" s="2">
-        <v>601</v>
-      </c>
-      <c r="E72" s="2">
-        <v>739</v>
-      </c>
-      <c r="F72" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G72" s="2">
-        <v>46</v>
-      </c>
-      <c r="H72" s="2">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D73" s="2">
-        <v>644</v>
-      </c>
-      <c r="E73" s="2">
-        <v>739</v>
-      </c>
-      <c r="F73" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G73" s="2">
-        <v>40</v>
-      </c>
-      <c r="H73" s="2">
-        <v>30</v>
-      </c>
-      <c r="I73" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="2">
-        <v>601</v>
-      </c>
-      <c r="E74" s="2">
-        <v>739</v>
-      </c>
-      <c r="F74" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G74" s="2">
-        <v>46</v>
-      </c>
-      <c r="H74" s="2">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D75" s="2">
-        <v>601</v>
-      </c>
-      <c r="E75" s="2">
-        <v>739</v>
-      </c>
-      <c r="F75" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G75" s="2">
-        <v>46</v>
-      </c>
-      <c r="H75" s="2">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="2">
-        <v>644</v>
-      </c>
-      <c r="E76" s="2">
-        <v>739</v>
-      </c>
-      <c r="F76" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G76" s="2">
-        <v>40</v>
-      </c>
-      <c r="H76" s="2">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D77" s="2">
-        <v>684</v>
-      </c>
-      <c r="E77" s="2">
-        <v>739</v>
-      </c>
-      <c r="F77" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G77" s="2">
-        <v>40</v>
-      </c>
-      <c r="H77" s="2">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" s="2">
-        <v>601</v>
-      </c>
-      <c r="E78" s="2">
-        <v>739</v>
-      </c>
-      <c r="F78" s="2">
-        <v>-138</v>
-      </c>
-      <c r="G78" s="2">
-        <v>46</v>
-      </c>
-      <c r="H78" s="2">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D79" s="2">
-        <v>644</v>
-      </c>
-      <c r="E79" s="2">
-        <v>739</v>
-      </c>
-      <c r="F79" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G79" s="2">
-        <v>40</v>
-      </c>
-      <c r="H79" s="2">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D80" s="2">
-        <v>644</v>
-      </c>
-      <c r="E80" s="2">
-        <v>739</v>
-      </c>
-      <c r="F80" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G80" s="2">
-        <v>40</v>
-      </c>
-      <c r="H80" s="2">
-        <v>30</v>
-      </c>
-      <c r="I80" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="2">
-        <v>684</v>
-      </c>
-      <c r="E81" s="2">
-        <v>739</v>
-      </c>
-      <c r="F81" s="2">
-        <v>-55</v>
-      </c>
-      <c r="G81" s="2">
-        <v>40</v>
-      </c>
-      <c r="H81" s="2">
-        <v>30</v>
-      </c>
-      <c r="I81" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D82" s="2">
-        <v>644</v>
-      </c>
-      <c r="E82" s="2">
-        <v>739</v>
-      </c>
-      <c r="F82" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G82" s="2">
-        <v>40</v>
-      </c>
-      <c r="H82" s="2">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D83" s="2">
-        <v>644</v>
-      </c>
-      <c r="E83" s="2">
-        <v>739</v>
-      </c>
-      <c r="F83" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G83" s="2">
-        <v>40</v>
-      </c>
-      <c r="H83" s="2">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="2">
-        <v>644</v>
-      </c>
-      <c r="E84" s="2">
-        <v>739</v>
-      </c>
-      <c r="F84" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G84" s="2">
-        <v>40</v>
-      </c>
-      <c r="H84" s="2">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D85" s="2">
-        <v>638</v>
-      </c>
-      <c r="E85" s="2">
-        <v>739</v>
-      </c>
-      <c r="F85" s="2">
-        <v>-101</v>
-      </c>
-      <c r="G85" s="2">
-        <v>46</v>
-      </c>
-      <c r="H85" s="2">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D86" s="2">
-        <v>644</v>
-      </c>
-      <c r="E86" s="2">
-        <v>739</v>
-      </c>
-      <c r="F86" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G86" s="2">
-        <v>40</v>
-      </c>
-      <c r="H86" s="2">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D87" s="2">
-        <v>679</v>
-      </c>
-      <c r="E87" s="2">
-        <v>739</v>
-      </c>
-      <c r="F87" s="2">
-        <v>-60</v>
-      </c>
-      <c r="G87" s="2">
-        <v>40</v>
-      </c>
-      <c r="H87" s="2">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D88" s="2">
-        <v>644</v>
-      </c>
-      <c r="E88" s="2">
-        <v>739</v>
-      </c>
-      <c r="F88" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G88" s="2">
-        <v>40</v>
-      </c>
-      <c r="H88" s="2">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D89" s="2">
-        <v>644</v>
-      </c>
-      <c r="E89" s="2">
-        <v>739</v>
-      </c>
-      <c r="F89" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G89" s="2">
-        <v>40</v>
-      </c>
-      <c r="H89" s="2">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90" s="2">
-        <v>644</v>
-      </c>
-      <c r="E90" s="2">
-        <v>739</v>
-      </c>
-      <c r="F90" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G90" s="2">
-        <v>40</v>
-      </c>
-      <c r="H90" s="2">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D91" s="2">
-        <v>644</v>
-      </c>
-      <c r="E91" s="2">
-        <v>739</v>
-      </c>
-      <c r="F91" s="2">
-        <v>-95</v>
-      </c>
-      <c r="G91" s="2">
-        <v>40</v>
-      </c>
-      <c r="H91" s="2">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D92" s="2">
-        <v>678</v>
-      </c>
-      <c r="E92" s="2">
-        <v>739</v>
-      </c>
-      <c r="F92" s="2">
-        <v>-61</v>
-      </c>
-      <c r="G92" s="2">
-        <v>40</v>
-      </c>
-      <c r="H92" s="2">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K92" s="2" t="s">
         <v>15</v>
       </c>
     </row>
